--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487408_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487408_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5.3029</v>
+        <v>6.1459</v>
       </c>
       <c r="E2" t="n">
-        <v>4.1696</v>
+        <v>4.6384</v>
       </c>
       <c r="F2" t="n">
-        <v>1.1333</v>
+        <v>1.5075</v>
       </c>
       <c r="G2" t="n">
         <v>6.131</v>
@@ -610,13 +610,13 @@
         <v>2.3502</v>
       </c>
       <c r="S2" t="n">
-        <v>-2.0654</v>
+        <v>-1.2224</v>
       </c>
       <c r="T2" t="n">
-        <v>-1.0339</v>
+        <v>-0.5652</v>
       </c>
       <c r="U2" t="n">
-        <v>-1.0315</v>
+        <v>-0.6572</v>
       </c>
       <c r="V2" t="n">
         <v>1.8249</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.5157</v>
+        <v>2.3156</v>
       </c>
       <c r="E3" t="n">
-        <v>1.1726</v>
+        <v>0.8656</v>
       </c>
       <c r="F3" t="n">
-        <v>1.3431</v>
+        <v>1.4501</v>
       </c>
       <c r="G3" t="n">
         <v>0.8416</v>
@@ -688,13 +688,13 @@
         <v>0.3917</v>
       </c>
       <c r="S3" t="n">
-        <v>0.08890000000000001</v>
+        <v>-0.1112</v>
       </c>
       <c r="T3" t="n">
-        <v>0.2664</v>
+        <v>-0.0406</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.1775</v>
+        <v>-0.0706</v>
       </c>
       <c r="V3" t="n">
         <v>1.3894</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.9906</v>
+        <v>1.979</v>
       </c>
       <c r="E4" t="n">
-        <v>3.3266</v>
+        <v>3.1813</v>
       </c>
       <c r="F4" t="n">
-        <v>-1.3359</v>
+        <v>-1.2023</v>
       </c>
       <c r="G4" t="n">
         <v>3.2725</v>
@@ -766,13 +766,13 @@
         <v>0.5875</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.8901</v>
+        <v>-0.9018</v>
       </c>
       <c r="T4" t="n">
-        <v>0.3017</v>
+        <v>0.1564</v>
       </c>
       <c r="U4" t="n">
-        <v>-1.1919</v>
+        <v>-1.0582</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.3888</v>
+        <v>0.4553</v>
       </c>
       <c r="E5" t="n">
-        <v>-1.5292</v>
+        <v>-1.9815</v>
       </c>
       <c r="F5" t="n">
-        <v>2.918</v>
+        <v>2.4368</v>
       </c>
       <c r="G5" t="n">
         <v>1.3255</v>
@@ -844,13 +844,13 @@
         <v>0.7834</v>
       </c>
       <c r="S5" t="n">
-        <v>0.7902</v>
+        <v>-0.1432</v>
       </c>
       <c r="T5" t="n">
-        <v>0.6869</v>
+        <v>0.2347</v>
       </c>
       <c r="U5" t="n">
-        <v>0.1033</v>
+        <v>-0.3779</v>
       </c>
       <c r="V5" t="n">
         <v>0.4481</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.1007</v>
+        <v>-0.07389999999999999</v>
       </c>
       <c r="E6" t="n">
         <v>0.0204</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.1211</v>
+        <v>-0.0944</v>
       </c>
       <c r="G6" t="n">
         <v>0.5662</v>
@@ -922,13 +922,13 @@
         <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.3915</v>
+        <v>-0.3648</v>
       </c>
       <c r="T6" t="n">
         <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.3915</v>
+        <v>-0.3648</v>
       </c>
       <c r="V6" t="n">
         <v>-0.2754</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A. GONZALEZ CORDERO</t>
+          <t>J. FERNÁNDEZ DEL RÍO</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.3459</v>
+        <v>-0.2166</v>
       </c>
       <c r="E7" t="n">
-        <v>-2.5886</v>
+        <v>-0.9004</v>
       </c>
       <c r="F7" t="n">
-        <v>2.2427</v>
+        <v>0.6838</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.5479000000000001</v>
+        <v>1.146</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.0429</v>
+        <v>-0.966</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.505</v>
+        <v>2.112</v>
       </c>
       <c r="J7" t="n">
-        <v>0.4406</v>
+        <v>0.7335</v>
       </c>
       <c r="K7" t="n">
-        <v>0.8352000000000001</v>
+        <v>-0.5597</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.3945</v>
+        <v>1.2933</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.9886</v>
+        <v>0.4125</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.8781</v>
+        <v>-0.4062</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.1105</v>
+        <v>0.8187</v>
       </c>
       <c r="P7" t="n">
-        <v>0.3917</v>
+        <v>-0.3917</v>
       </c>
       <c r="Q7" t="n">
-        <v>-2.1543</v>
+        <v>-0.9792</v>
       </c>
       <c r="R7" t="n">
-        <v>2.546</v>
+        <v>0.5875</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.7403999999999999</v>
+        <v>-0.0297</v>
       </c>
       <c r="T7" t="n">
-        <v>-1.4256</v>
+        <v>0.0112</v>
       </c>
       <c r="U7" t="n">
-        <v>0.6852</v>
+        <v>-0.0409</v>
       </c>
       <c r="V7" t="n">
-        <v>0.5507</v>
+        <v>-0.9412</v>
       </c>
       <c r="W7" t="n">
-        <v>0.5507</v>
+        <v>-0.6659</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>-0.2754</v>
       </c>
     </row>
     <row r="8">
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.4965</v>
+        <v>-0.2467</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.6238</v>
+        <v>-1.8285</v>
       </c>
       <c r="F8" t="n">
-        <v>1.1273</v>
+        <v>1.5818</v>
       </c>
       <c r="G8" t="n">
         <v>1.5572</v>
@@ -1078,13 +1078,13 @@
         <v>2.3502</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.2703</v>
+        <v>-1.0206</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.5652</v>
+        <v>-0.7699</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.7050999999999999</v>
+        <v>-0.2507</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>J. FERNÁNDEZ DEL RÍO</t>
+          <t>A. GONZALEZ CORDERO</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.8933</v>
+        <v>-0.6966</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.3098</v>
+        <v>-2.3246</v>
       </c>
       <c r="F9" t="n">
-        <v>0.4165</v>
+        <v>1.6279</v>
       </c>
       <c r="G9" t="n">
-        <v>1.146</v>
+        <v>-0.5479000000000001</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.966</v>
+        <v>-0.0429</v>
       </c>
       <c r="I9" t="n">
-        <v>2.112</v>
+        <v>-0.505</v>
       </c>
       <c r="J9" t="n">
-        <v>0.7335</v>
+        <v>0.4406</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.5597</v>
+        <v>0.8352000000000001</v>
       </c>
       <c r="L9" t="n">
-        <v>1.2933</v>
+        <v>-0.3945</v>
       </c>
       <c r="M9" t="n">
-        <v>0.4125</v>
+        <v>-0.9886</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.4062</v>
+        <v>-0.8781</v>
       </c>
       <c r="O9" t="n">
-        <v>0.8187</v>
+        <v>-0.1105</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.3917</v>
+        <v>0.3917</v>
       </c>
       <c r="Q9" t="n">
-        <v>-0.9792</v>
+        <v>-2.1543</v>
       </c>
       <c r="R9" t="n">
-        <v>0.5875</v>
+        <v>2.546</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.7064</v>
+        <v>-1.0911</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.3982</v>
+        <v>-1.1616</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.3082</v>
+        <v>0.0704</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.9412</v>
+        <v>0.5507</v>
       </c>
       <c r="W9" t="n">
-        <v>-0.6659</v>
+        <v>0.5507</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.2754</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.2315</v>
+        <v>-1.4583</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.64</v>
+        <v>-0.947</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.5914</v>
+        <v>-0.5112</v>
       </c>
       <c r="G10" t="n">
         <v>0.6316000000000001</v>
@@ -1234,13 +1234,13 @@
         <v>2.1543</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.6257</v>
+        <v>-1.8525</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.4705</v>
+        <v>-0.7775</v>
       </c>
       <c r="U10" t="n">
-        <v>-1.1551</v>
+        <v>-1.075</v>
       </c>
       <c r="V10" t="n">
         <v>-1.2166</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.5929</v>
+        <v>-2.3693</v>
       </c>
       <c r="E11" t="n">
-        <v>-4.8335</v>
+        <v>-4.2625</v>
       </c>
       <c r="F11" t="n">
-        <v>2.2407</v>
+        <v>1.8932</v>
       </c>
       <c r="G11" t="n">
         <v>0.284</v>
@@ -1312,13 +1312,13 @@
         <v>2.9377</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.4644</v>
+        <v>-1.2408</v>
       </c>
       <c r="T11" t="n">
-        <v>-1.408</v>
+        <v>-0.8369</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.0564</v>
+        <v>-0.4039</v>
       </c>
       <c r="V11" t="n">
         <v>-1.2166</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>5.5372</v>
+        <v>5.834400000000001</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.835700000000001</v>
+        <v>-3.538800000000001</v>
       </c>
       <c r="F12" t="n">
-        <v>9.373200000000001</v>
+        <v>9.373199999999999</v>
       </c>
       <c r="G12" t="n">
         <v>15.2077</v>
@@ -1372,7 +1372,7 @@
         <v>9.947900000000001</v>
       </c>
       <c r="M12" t="n">
-        <v>1.551599999999999</v>
+        <v>1.5516</v>
       </c>
       <c r="N12" t="n">
         <v>-1.9895</v>
@@ -1390,13 +1390,13 @@
         <v>14.6885</v>
       </c>
       <c r="S12" t="n">
-        <v>-8.2751</v>
+        <v>-7.9781</v>
       </c>
       <c r="T12" t="n">
-        <v>-4.0464</v>
+        <v>-3.7494</v>
       </c>
       <c r="U12" t="n">
-        <v>-4.2287</v>
+        <v>-4.2288</v>
       </c>
       <c r="V12" t="n">
         <v>0.5632999999999999</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>2.998</v>
+        <v>3.139</v>
       </c>
       <c r="E13" t="n">
-        <v>1.8917</v>
+        <v>1.7894</v>
       </c>
       <c r="F13" t="n">
-        <v>1.1063</v>
+        <v>1.3497</v>
       </c>
       <c r="G13" t="n">
         <v>1.2288</v>
@@ -1468,13 +1468,13 @@
         <v>1.9585</v>
       </c>
       <c r="S13" t="n">
-        <v>1.1805</v>
+        <v>1.3215</v>
       </c>
       <c r="T13" t="n">
-        <v>0.7046</v>
+        <v>0.6022</v>
       </c>
       <c r="U13" t="n">
-        <v>0.4759</v>
+        <v>0.7193000000000001</v>
       </c>
       <c r="V13" t="n">
         <v>-0.3905</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>S. RODRÍGUEZ TAPIA</t>
+          <t>Á. SONEIRA BOO</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>1.9739</v>
+        <v>2.3361</v>
       </c>
       <c r="E14" t="n">
-        <v>1.4671</v>
+        <v>1.5093</v>
       </c>
       <c r="F14" t="n">
-        <v>0.5068</v>
+        <v>0.8268</v>
       </c>
       <c r="G14" t="n">
-        <v>1.4767</v>
+        <v>-0.102</v>
       </c>
       <c r="H14" t="n">
-        <v>1.9105</v>
+        <v>-1.7942</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.4338</v>
+        <v>1.6922</v>
       </c>
       <c r="J14" t="n">
-        <v>2.26</v>
+        <v>1.0334</v>
       </c>
       <c r="K14" t="n">
-        <v>2.1792</v>
+        <v>-1.3203</v>
       </c>
       <c r="L14" t="n">
-        <v>0.0808</v>
+        <v>2.3537</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.7834</v>
+        <v>-1.1354</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.2687</v>
+        <v>-0.4739</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.5145999999999999</v>
+        <v>-0.6615</v>
       </c>
       <c r="P14" t="n">
-        <v>0.1958</v>
+        <v>1.3709</v>
       </c>
       <c r="Q14" t="n">
-        <v>-1.9585</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>2.1543</v>
+        <v>1.3709</v>
       </c>
       <c r="S14" t="n">
-        <v>1.518</v>
+        <v>0.7917999999999999</v>
       </c>
       <c r="T14" t="n">
-        <v>1.8314</v>
+        <v>0.2005</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.3134</v>
+        <v>0.5911999999999999</v>
       </c>
       <c r="V14" t="n">
-        <v>-1.2166</v>
+        <v>0.2754</v>
       </c>
       <c r="W14" t="n">
-        <v>-0.6659</v>
+        <v>0.2754</v>
       </c>
       <c r="X14" t="n">
-        <v>-0.5507</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Á. SONEIRA BOO</t>
+          <t>S. RODRÍGUEZ TAPIA</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.4372</v>
+        <v>1.5129</v>
       </c>
       <c r="E15" t="n">
-        <v>0.6906</v>
+        <v>0.5461</v>
       </c>
       <c r="F15" t="n">
-        <v>0.7466</v>
+        <v>0.9668</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.102</v>
+        <v>1.4767</v>
       </c>
       <c r="H15" t="n">
-        <v>-1.7942</v>
+        <v>1.9105</v>
       </c>
       <c r="I15" t="n">
-        <v>1.6922</v>
+        <v>-0.4338</v>
       </c>
       <c r="J15" t="n">
-        <v>1.0334</v>
+        <v>2.26</v>
       </c>
       <c r="K15" t="n">
-        <v>-1.3203</v>
+        <v>2.1792</v>
       </c>
       <c r="L15" t="n">
-        <v>2.3537</v>
+        <v>0.0808</v>
       </c>
       <c r="M15" t="n">
-        <v>-1.1354</v>
+        <v>-0.7834</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.4739</v>
+        <v>-0.2687</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.6615</v>
+        <v>-0.5145999999999999</v>
       </c>
       <c r="P15" t="n">
-        <v>1.3709</v>
+        <v>0.1958</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>-1.9585</v>
       </c>
       <c r="R15" t="n">
-        <v>1.3709</v>
+        <v>2.1543</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.1071</v>
+        <v>1.057</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.6181</v>
+        <v>0.9104</v>
       </c>
       <c r="U15" t="n">
-        <v>0.511</v>
+        <v>0.1466</v>
       </c>
       <c r="V15" t="n">
-        <v>0.2754</v>
+        <v>-1.2166</v>
       </c>
       <c r="W15" t="n">
-        <v>0.2754</v>
+        <v>-0.6659</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>-0.5507</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>G. GONZALEZ GARCIA</t>
+          <t>N. FUENTES PRADO</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,64 +1657,64 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.0757</v>
+        <v>-0.0339</v>
       </c>
       <c r="E16" t="n">
-        <v>-1.1645</v>
+        <v>0.2694</v>
       </c>
       <c r="F16" t="n">
-        <v>1.2402</v>
+        <v>-0.3033</v>
       </c>
       <c r="G16" t="n">
-        <v>-3.9379</v>
+        <v>-0.4625</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.0021</v>
+        <v>-0.5029</v>
       </c>
       <c r="I16" t="n">
-        <v>-3.9358</v>
+        <v>0.0404</v>
       </c>
       <c r="J16" t="n">
-        <v>-2.2744</v>
+        <v>0.08119999999999999</v>
       </c>
       <c r="K16" t="n">
-        <v>0.3333</v>
+        <v>0.0408</v>
       </c>
       <c r="L16" t="n">
-        <v>-2.6077</v>
+        <v>0.0404</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.6635</v>
+        <v>-0.5437</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.3354</v>
+        <v>-0.5437</v>
       </c>
       <c r="O16" t="n">
-        <v>-1.3281</v>
+        <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>0.9792</v>
+        <v>0.1958</v>
       </c>
       <c r="Q16" t="n">
-        <v>-0.9792</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>1.9585</v>
+        <v>0.1958</v>
       </c>
       <c r="S16" t="n">
-        <v>2.759</v>
+        <v>0.2328</v>
       </c>
       <c r="T16" t="n">
-        <v>1.8138</v>
+        <v>0.1882</v>
       </c>
       <c r="U16" t="n">
-        <v>0.9452</v>
+        <v>0.0446</v>
       </c>
       <c r="V16" t="n">
-        <v>0.2754</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>0.2754</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
         <v>0</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>F. CORNALIS</t>
+          <t>G. GONZALEZ GARCIA</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,64 +1735,64 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.4677</v>
+        <v>-0.448</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.0594</v>
+        <v>-1.8808</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.4083</v>
+        <v>1.4329</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.4083</v>
+        <v>-3.9379</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.4083</v>
+        <v>-0.0021</v>
       </c>
       <c r="I17" t="n">
-        <v>0</v>
+        <v>-3.9358</v>
       </c>
       <c r="J17" t="n">
-        <v>0</v>
+        <v>-2.2744</v>
       </c>
       <c r="K17" t="n">
-        <v>0</v>
+        <v>0.3333</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>-2.6077</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.4083</v>
+        <v>-1.6635</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.4083</v>
+        <v>-0.3354</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>-1.3281</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>0.9792</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>-0.9792</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>1.9585</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.0594</v>
+        <v>2.2354</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.0594</v>
+        <v>1.0975</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>1.1379</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>0.2754</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>0.2754</v>
       </c>
       <c r="X17" t="n">
         <v>0</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>N. FUENTES PRADO</t>
+          <t>F. CORNALIS</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,58 +1813,58 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.504</v>
+        <v>-0.4677</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.0376</v>
+        <v>-0.0594</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.4665</v>
+        <v>-0.4083</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.4625</v>
+        <v>-0.4083</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.5029</v>
+        <v>-0.4083</v>
       </c>
       <c r="I18" t="n">
-        <v>0.0404</v>
+        <v>0</v>
       </c>
       <c r="J18" t="n">
-        <v>0.08119999999999999</v>
+        <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>0.0408</v>
+        <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>0.0404</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.5437</v>
+        <v>-0.4083</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.5437</v>
+        <v>-0.4083</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>0.1958</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>0.1958</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.2374</v>
+        <v>-0.0594</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.1188</v>
+        <v>-0.0594</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.1186</v>
+        <v>0</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.3473</v>
+        <v>-1.3094</v>
       </c>
       <c r="E19" t="n">
-        <v>-2.3235</v>
+        <v>-1.9141</v>
       </c>
       <c r="F19" t="n">
-        <v>0.9761</v>
+        <v>0.6047</v>
       </c>
       <c r="G19" t="n">
         <v>-4.2283</v>
@@ -1936,13 +1936,13 @@
         <v>2.7419</v>
       </c>
       <c r="S19" t="n">
-        <v>1.8222</v>
+        <v>1.8601</v>
       </c>
       <c r="T19" t="n">
-        <v>0.17</v>
+        <v>0.5793</v>
       </c>
       <c r="U19" t="n">
-        <v>1.6523</v>
+        <v>1.2808</v>
       </c>
       <c r="V19" t="n">
         <v>0.2754</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.7349</v>
+        <v>-1.3227</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.7732</v>
+        <v>-1.3639</v>
       </c>
       <c r="F20" t="n">
-        <v>0.0384</v>
+        <v>0.0412</v>
       </c>
       <c r="G20" t="n">
         <v>-2.625</v>
@@ -2014,13 +2014,13 @@
         <v>1.5668</v>
       </c>
       <c r="S20" t="n">
-        <v>0.3026</v>
+        <v>0.7147</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.1141</v>
+        <v>0.2952</v>
       </c>
       <c r="U20" t="n">
-        <v>0.4167</v>
+        <v>0.4195</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.1232</v>
+        <v>-1.8366</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.3189</v>
+        <v>-2.6259</v>
       </c>
       <c r="F21" t="n">
-        <v>0.1957</v>
+        <v>0.7893</v>
       </c>
       <c r="G21" t="n">
         <v>-4.3043</v>
@@ -2092,13 +2092,13 @@
         <v>2.3502</v>
       </c>
       <c r="S21" t="n">
-        <v>1.3342</v>
+        <v>1.6209</v>
       </c>
       <c r="T21" t="n">
-        <v>1.1492</v>
+        <v>0.8421999999999999</v>
       </c>
       <c r="U21" t="n">
-        <v>0.185</v>
+        <v>0.7786999999999999</v>
       </c>
       <c r="V21" t="n">
         <v>1.4344</v>
@@ -2113,7 +2113,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Y. PINAS</t>
+          <t>T. MARTINEZ CARRO</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.7943</v>
+        <v>-2.846</v>
       </c>
       <c r="E22" t="n">
-        <v>-3.0069</v>
+        <v>-2.5339</v>
       </c>
       <c r="F22" t="n">
-        <v>0.2126</v>
+        <v>-0.3121</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.42</v>
+        <v>-1.4247</v>
       </c>
       <c r="H22" t="n">
-        <v>0.3375</v>
+        <v>-0.1215</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.7575</v>
+        <v>-1.3033</v>
       </c>
       <c r="J22" t="n">
-        <v>0.6477000000000001</v>
+        <v>-1.2424</v>
       </c>
       <c r="K22" t="n">
-        <v>0.6073</v>
+        <v>-0.6006</v>
       </c>
       <c r="L22" t="n">
-        <v>0.0404</v>
+        <v>-0.6418</v>
       </c>
       <c r="M22" t="n">
-        <v>-1.0677</v>
+        <v>-0.1823</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.2698</v>
+        <v>0.4791</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.7979000000000001</v>
+        <v>-0.6615</v>
       </c>
       <c r="P22" t="n">
-        <v>-2.546</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>-3.917</v>
+        <v>-0.9792</v>
       </c>
       <c r="R22" t="n">
-        <v>1.3709</v>
+        <v>0.9792</v>
       </c>
       <c r="S22" t="n">
-        <v>0.1717</v>
+        <v>-0.2047</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.0129</v>
+        <v>-0.3123</v>
       </c>
       <c r="U22" t="n">
-        <v>0.1847</v>
+        <v>0.1076</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>-1.2166</v>
       </c>
       <c r="W22" t="n">
-        <v>0.2754</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-0.2754</v>
+        <v>-1.2166</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>T. MARTINEZ CARRO</t>
+          <t>Y. PINAS</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.0507</v>
+        <v>-2.8967</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.7386</v>
+        <v>-3.1092</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.3121</v>
+        <v>0.2126</v>
       </c>
       <c r="G23" t="n">
-        <v>-1.4247</v>
+        <v>-0.42</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.1215</v>
+        <v>0.3375</v>
       </c>
       <c r="I23" t="n">
-        <v>-1.3033</v>
+        <v>-0.7575</v>
       </c>
       <c r="J23" t="n">
-        <v>-1.2424</v>
+        <v>0.6477000000000001</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.6006</v>
+        <v>0.6073</v>
       </c>
       <c r="L23" t="n">
-        <v>-0.6418</v>
+        <v>0.0404</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.1823</v>
+        <v>-1.0677</v>
       </c>
       <c r="N23" t="n">
-        <v>0.4791</v>
+        <v>-0.2698</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.6615</v>
+        <v>-0.7979000000000001</v>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>-2.546</v>
       </c>
       <c r="Q23" t="n">
-        <v>-0.9792</v>
+        <v>-3.917</v>
       </c>
       <c r="R23" t="n">
-        <v>0.9792</v>
+        <v>1.3709</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.4093</v>
+        <v>0.0694</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.517</v>
+        <v>-0.1153</v>
       </c>
       <c r="U23" t="n">
-        <v>0.1076</v>
+        <v>0.1847</v>
       </c>
       <c r="V23" t="n">
-        <v>-1.2166</v>
+        <v>0</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>0.2754</v>
       </c>
       <c r="X23" t="n">
-        <v>-1.2166</v>
+        <v>-0.2754</v>
       </c>
     </row>
     <row r="24">
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-5.5373</v>
+        <v>-4.173</v>
       </c>
       <c r="E24" t="n">
-        <v>-9.373200000000001</v>
+        <v>-9.372999999999999</v>
       </c>
       <c r="F24" t="n">
-        <v>3.8358</v>
+        <v>5.2003</v>
       </c>
       <c r="G24" t="n">
         <v>-15.2075</v>
@@ -2299,10 +2299,10 @@
         <v>-13.489</v>
       </c>
       <c r="J24" t="n">
-        <v>-1.551499999999999</v>
+        <v>-1.5515</v>
       </c>
       <c r="K24" t="n">
-        <v>1.9894</v>
+        <v>1.989399999999999</v>
       </c>
       <c r="L24" t="n">
         <v>-3.541</v>
@@ -2311,13 +2311,13 @@
         <v>-13.6561</v>
       </c>
       <c r="N24" t="n">
-        <v>-3.707999999999999</v>
+        <v>-3.708</v>
       </c>
       <c r="O24" t="n">
-        <v>-9.948000000000002</v>
+        <v>-9.948</v>
       </c>
       <c r="P24" t="n">
-        <v>1.9583</v>
+        <v>1.958299999999999</v>
       </c>
       <c r="Q24" t="n">
         <v>-14.6885</v>
@@ -2326,16 +2326,16 @@
         <v>16.647</v>
       </c>
       <c r="S24" t="n">
-        <v>8.275</v>
+        <v>9.6395</v>
       </c>
       <c r="T24" t="n">
-        <v>4.228699999999999</v>
+        <v>4.228499999999999</v>
       </c>
       <c r="U24" t="n">
-        <v>4.046399999999999</v>
+        <v>5.4109</v>
       </c>
       <c r="V24" t="n">
-        <v>-0.5631</v>
+        <v>-0.5630999999999999</v>
       </c>
       <c r="W24" t="n">
         <v>2.6386</v>
